--- a/Configs/GameConfig/Datas/fg/#RemovedContent-已移除内容.xlsx
+++ b/Configs/GameConfig/Datas/fg/#RemovedContent-已移除内容.xlsx
@@ -493,7 +493,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>内容类别:primitive_chip</t>
+          <t>内容类别:primitive_chip/building</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">

--- a/Configs/GameConfig/Datas/fg/#RemovedContent-已移除内容.xlsx
+++ b/Configs/GameConfig/Datas/fg/#RemovedContent-已移除内容.xlsx
@@ -493,7 +493,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>内容类别:primitive_chip/building</t>
+          <t>内容类别:primitive_chip/building/analysis</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">

--- a/Configs/GameConfig/Datas/fg/#RemovedContent-已移除内容.xlsx
+++ b/Configs/GameConfig/Datas/fg/#RemovedContent-已移除内容.xlsx
@@ -493,7 +493,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>内容类别:primitive_chip/building/analysis</t>
+          <t>内容类别:primitive_chip/building/analysis/quest_item</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
